--- a/utils/similarity_tmmis.xlsx
+++ b/utils/similarity_tmmis.xlsx
@@ -19263,7 +19263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC29"/>
+  <dimension ref="A1:AD30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19279,130 +19279,135 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Rachel Chernos Lin</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Jamaal Myers</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Ausma Malik</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Alejandra Bravo</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Amber Morley</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Chris Moise</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Shelley Carroll</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Gord Perks</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Josh Matlow</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Jennifer McKelvie</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Amber Morley</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Gord Perks</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Shelley Carroll</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Josh Matlow</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Paul Ainslie</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Paula Fletcher</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Paul Ainslie</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Dianne Saxe</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Mike Colle</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Lily Cheng</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Parthi Kandavel</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Lily Cheng</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Mike Colle</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Michael Thompson</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Frances Nunziata</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Nick Mantas</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Anthony Perruzza</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Jon Burnside</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Anthony Perruzza</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>James Pasternak</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Vincent Crisanti</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Jaye Robinson</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Brad Bradford</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Vincent Crisanti</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Stephen Holyday</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>John Tory</t>
         </is>
@@ -19421,81 +19426,84 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9463806970509383</v>
+        <v>0.95625</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9430051813471503</v>
+        <v>0.9526411657559198</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9381443298969072</v>
+        <v>0.9425087108013938</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9247311827956989</v>
+        <v>0.9320214669051878</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9202279202279202</v>
+        <v>0.9269565217391305</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9192708333333334</v>
+        <v>0.9256637168141593</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9181585677749361</v>
+        <v>0.9184466019417475</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9178082191780822</v>
+        <v>0.9165247018739353</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9135135135135135</v>
+        <v>0.9142857142857143</v>
       </c>
       <c r="M2" t="n">
-        <v>0.898876404494382</v>
+        <v>0.9122448979591837</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8976608187134503</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8864864864864865</v>
+        <v>0.908411214953271</v>
       </c>
       <c r="P2" t="n">
-        <v>0.8830188679245283</v>
+        <v>0.8851224105461394</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.8643617021276596</v>
+        <v>0.8667953667953667</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8579387186629527</v>
+        <v>0.8665480427046264</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8453237410071942</v>
+        <v>0.8646788990825688</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8149100257069408</v>
+        <v>0.8538461538461538</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8068181818181819</v>
+        <v>0.8490566037735849</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7594202898550725</v>
+        <v>0.7893700787401575</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7409470752089137</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="X2" t="n">
-        <v>0.7048710601719197</v>
+        <v>0.724907063197026</v>
       </c>
       <c r="Y2" t="n">
+        <v>0.7151051625239006</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.6943127962085308</v>
+      </c>
+      <c r="AA2" t="n">
         <v>0.6787564766839378</v>
       </c>
-      <c r="Z2" t="n">
-        <v>0.6780626780626781</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0.667844522968198</v>
-      </c>
       <c r="AB2" t="n">
-        <v>0.268542199488491</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
+        <v>0.6600397614314115</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.2589437819420783</v>
+      </c>
+      <c r="AD2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -19509,809 +19517,828 @@
       <c r="C3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
         <v>0.7227272727272727</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>0.641255605381166</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>0.6339285714285714</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
+        <v>0.7123893805309734</v>
+      </c>
+      <c r="I3" t="n">
         <v>0.7256637168141593</v>
       </c>
-      <c r="H3" t="n">
-        <v>0.8533333333333333</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.7123893805309734</v>
-      </c>
       <c r="J3" t="n">
+        <v>0.7678571428571428</v>
+      </c>
+      <c r="K3" t="n">
         <v>0.5982142857142857</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.7678571428571428</v>
       </c>
       <c r="L3" t="n">
         <v>0.5669642857142857</v>
       </c>
       <c r="M3" t="n">
-        <v>0.663677130044843</v>
+        <v>0.8533333333333333</v>
       </c>
       <c r="N3" t="n">
         <v>0.8310502283105023</v>
       </c>
       <c r="O3" t="n">
+        <v>0.663677130044843</v>
+      </c>
+      <c r="P3" t="n">
         <v>0.7136363636363636</v>
       </c>
-      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
+        <v>0.7014218009478673</v>
+      </c>
+      <c r="R3" t="n">
         <v>0.7195767195767195</v>
       </c>
-      <c r="R3" t="n">
-        <v>0.7014218009478673</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="n">
         <v>0.817351598173516</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>0.875</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>0.8403755868544601</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.755868544600939</v>
       </c>
       <c r="W3" t="n">
         <v>0.7014218009478673</v>
       </c>
       <c r="X3" t="n">
+        <v>0.755868544600939</v>
+      </c>
+      <c r="Y3" t="n">
         <v>0.778894472361809</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
+        <v>0.8634146341463415</v>
+      </c>
+      <c r="AA3" t="n">
         <v>0.7136363636363636</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AB3" t="n">
         <v>0.8486238532110092</v>
       </c>
-      <c r="AA3" t="n">
-        <v>0.8634146341463415</v>
-      </c>
-      <c r="AB3" t="n">
+      <c r="AC3" t="n">
         <v>0.5663716814159292</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AD3" t="n">
         <v>0.9263157894736842</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Jamaal Myers</t>
+          <t>Rachel Chernos Lin</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9463806970509383</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.7227272727272727</v>
-      </c>
+        <v>0.95625</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9096296296296297</v>
+        <v>0.9235294117647059</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9109792284866469</v>
+        <v>0.8983050847457628</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8836140888208269</v>
+        <v>0.8881578947368421</v>
       </c>
       <c r="H4" t="n">
-        <v>0.878125</v>
+        <v>0.9152542372881356</v>
       </c>
       <c r="I4" t="n">
-        <v>0.898379970544919</v>
+        <v>0.8876404494382022</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8768328445747801</v>
+        <v>0.9</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8395638629283489</v>
+        <v>0.8743169398907104</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8432267884322679</v>
+        <v>0.8932584269662921</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8840125391849529</v>
+        <v>0.8738738738738738</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8596774193548387</v>
+        <v>0.8930817610062893</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8759571209800919</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8813559322033898</v>
+        <v>0.8493150684931507</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.864951768488746</v>
+        <v>0.9172413793103449</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7880258899676376</v>
+        <v>0.8681318681318682</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7710622710622711</v>
+        <v>0.8311688311688312</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7843426883308715</v>
+        <v>0.8211382113821138</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7814992025518341</v>
+        <v>0.8784530386740331</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7263843648208469</v>
+        <v>0.7730496453900709</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6942277691107644</v>
+        <v>0.7988505747126436</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6832191780821918</v>
+        <v>0.7183908045977012</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.6490066225165563</v>
+        <v>0.7469135802469136</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.7163695299837926</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0.6962962962962963</v>
-      </c>
+        <v>0.7258064516129032</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.6043165467625899</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.8526315789473684</v>
-      </c>
+        <v>0.2841530054644809</v>
+      </c>
+      <c r="AD4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Ausma Malik</t>
+          <t>Jamaal Myers</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9430051813471503</v>
+        <v>0.9526411657559198</v>
       </c>
       <c r="C5" t="n">
-        <v>0.641255605381166</v>
+        <v>0.7227272727272727</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9096296296296297</v>
+        <v>0.9235294117647059</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9624819624819625</v>
+        <v>0.9167630057803469</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8804185351270553</v>
+        <v>0.9135071090047393</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8269525267993875</v>
+        <v>0.9060710194730813</v>
       </c>
       <c r="I5" t="n">
-        <v>0.88328530259366</v>
+        <v>0.8879716981132075</v>
       </c>
       <c r="J5" t="n">
-        <v>0.927038626609442</v>
+        <v>0.8508217446270544</v>
       </c>
       <c r="K5" t="n">
-        <v>0.842185128983308</v>
+        <v>0.8786848072562359</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8722139673105498</v>
+        <v>0.8569753810082064</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9125766871165644</v>
+        <v>0.8753213367609255</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8526645768025078</v>
+        <v>0.8716981132075472</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8488023952095809</v>
+        <v>0.8910648714810282</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8446601941747574</v>
+        <v>0.8723926380368098</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8367346938775511</v>
+        <v>0.8066581306017926</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7804107424960506</v>
+        <v>0.8681318681318682</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7375886524822695</v>
+        <v>0.8565310492505354</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7363112391930835</v>
+        <v>0.7841079460269865</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7180685358255452</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6869009584664536</v>
+        <v>0.7735368956743003</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6804915514592934</v>
+        <v>0.7232250300842359</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6456953642384107</v>
+        <v>0.7151741293532339</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.6379310344827587</v>
+        <v>0.6981627296587927</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.665086887835703</v>
+        <v>0.7004405286343612</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.6290909090909091</v>
+        <v>0.6490066225165563</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2767475035663338</v>
+        <v>0.6971649484536082</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7065217391304348</v>
+        <v>0.3201357466063348</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.8526315789473684</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Alejandra Bravo</t>
+          <t>Ausma Malik</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9381443298969072</v>
+        <v>0.9425087108013938</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6339285714285714</v>
+        <v>0.641255605381166</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9109792284866469</v>
+        <v>0.8983050847457628</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9624819624819625</v>
+        <v>0.9167630057803469</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8839285714285714</v>
+        <v>0.9581447963800905</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8205521472392638</v>
+        <v>0.8853362734288864</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8760806916426513</v>
+        <v>0.8860045146726863</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9284692417739628</v>
+        <v>0.8576598311218335</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8389057750759878</v>
+        <v>0.9249183895538629</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8531157270029673</v>
+        <v>0.8816234498308906</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8953846153846154</v>
+        <v>0.8308457711442786</v>
       </c>
       <c r="N6" t="n">
-        <v>0.839622641509434</v>
+        <v>0.8658682634730539</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8473053892215568</v>
+        <v>0.9178403755868545</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8300653594771241</v>
+        <v>0.8525564803804995</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.8249211356466877</v>
+        <v>0.7992656058751531</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7772511848341233</v>
+        <v>0.8368794326241135</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7361853832442068</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7374461979913917</v>
+        <v>0.7612156295224313</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7165109034267914</v>
+        <v>0.7677984665936473</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6773162939297125</v>
+        <v>0.7200488997555012</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6625766871165644</v>
+        <v>0.7127906976744186</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6378737541528239</v>
+        <v>0.6830143540669856</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.6314655172413793</v>
+        <v>0.6662515566625156</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.6582677165354331</v>
+        <v>0.6481481481481481</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.6160877513711152</v>
+        <v>0.6379310344827587</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.2781740370898717</v>
+        <v>0.6458072590738423</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.7157894736842105</v>
+        <v>0.2736156351791531</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.7065217391304348</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Chris Moise</t>
+          <t>Alejandra Bravo</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9247311827956989</v>
+        <v>0.9320214669051878</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7256637168141593</v>
+        <v>0.6339285714285714</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8836140888208269</v>
+        <v>0.8881578947368421</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8804185351270553</v>
+        <v>0.9135071090047393</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8839285714285714</v>
+        <v>0.9581447963800905</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8609794628751974</v>
+        <v>0.8779661016949153</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8660714285714286</v>
+        <v>0.8833718244803695</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8788774002954209</v>
+        <v>0.8536285362853628</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8869701726844584</v>
+        <v>0.9319955406911928</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8064516129032258</v>
+        <v>0.8604382929642445</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8542319749216301</v>
+        <v>0.8209331651954603</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8444084278768234</v>
+        <v>0.8448484848484848</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8472222222222222</v>
+        <v>0.895808383233533</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8091872791519434</v>
+        <v>0.8491484184914841</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8150572831423896</v>
+        <v>0.79375</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7823240589198036</v>
+        <v>0.8197320341047503</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7948243992606285</v>
+        <v>0.8256302521008403</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7881481481481482</v>
+        <v>0.7540983606557377</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7588996763754046</v>
+        <v>0.7625979843225084</v>
       </c>
       <c r="V7" t="n">
-        <v>0.7168874172185431</v>
+        <v>0.71875</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6820349761526232</v>
+        <v>0.6868327402135231</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6734348561759729</v>
+        <v>0.6654366543665436</v>
       </c>
       <c r="Y7" t="n">
+        <v>0.6470588235294117</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.629737609329446</v>
+      </c>
+      <c r="AA7" t="n">
         <v>0.6314655172413793</v>
       </c>
-      <c r="Z7" t="n">
-        <v>0.7071197411003236</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0.666030534351145</v>
-      </c>
       <c r="AB7" t="n">
-        <v>0.3078055964653903</v>
+        <v>0.6304347826086957</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.8631578947368421</v>
+        <v>0.2669632925472748</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.7157894736842105</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Jennifer McKelvie</t>
+          <t>Amber Morley</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9202279202279202</v>
+        <v>0.9269565217391305</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8533333333333333</v>
+        <v>0.7123893805309734</v>
       </c>
       <c r="D8" t="n">
-        <v>0.878125</v>
+        <v>0.9152542372881356</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8269525267993875</v>
+        <v>0.9060710194730813</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8205521472392638</v>
+        <v>0.8853362734288864</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8609794628751974</v>
+        <v>0.8779661016949153</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8470948012232415</v>
+        <v>0.8773903262092239</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7981790591805766</v>
+        <v>0.8393285371702638</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8656</v>
+        <v>0.8593073593073592</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7870662460567823</v>
+        <v>0.8552188552188552</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8061889250814332</v>
+        <v>0.8546583850931677</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8592964824120604</v>
+        <v>0.8552631578947368</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8325434439178515</v>
+        <v>0.8755813953488372</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8641509433962264</v>
+        <v>0.8403755868544601</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8375209380234506</v>
+        <v>0.8086642599277978</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7949579831932774</v>
+        <v>0.8502358490566038</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8546845124282982</v>
+        <v>0.8560157790927021</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8669724770642202</v>
+        <v>0.8170028818443804</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8413223140495868</v>
+        <v>0.8015267175572519</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7804054054054054</v>
+        <v>0.7859733978234583</v>
       </c>
       <c r="W8" t="n">
-        <v>0.7079934747145187</v>
+        <v>0.7349537037037037</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7548500881834215</v>
+        <v>0.7035714285714285</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.7145969498910676</v>
+        <v>0.7235367372353674</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.7953410981697171</v>
+        <v>0.7102672292545711</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.7934362934362934</v>
+        <v>0.6609071274298056</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.3903177004538578</v>
+        <v>0.6811414392059554</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.9789473684210527</v>
+        <v>0.306695464362851</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.7789473684210526</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Amber Morley</t>
+          <t>Chris Moise</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9192708333333334</v>
+        <v>0.9256637168141593</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7123893805309734</v>
+        <v>0.7256637168141593</v>
       </c>
       <c r="D9" t="n">
-        <v>0.898379970544919</v>
+        <v>0.8876404494382022</v>
       </c>
       <c r="E9" t="n">
-        <v>0.88328530259366</v>
+        <v>0.8879716981132075</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8760806916426513</v>
+        <v>0.8860045146726863</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8660714285714286</v>
+        <v>0.8833718244803695</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8470948012232415</v>
+        <v>0.8773903262092239</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.858974358974359</v>
+        <v>0.8929889298892989</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8242424242424242</v>
+        <v>0.8802660753880266</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8444444444444444</v>
+        <v>0.8206896551724138</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8704268292682926</v>
+        <v>0.861323155216285</v>
       </c>
       <c r="N9" t="n">
-        <v>0.841692789968652</v>
+        <v>0.8580171358629131</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8330849478390462</v>
+        <v>0.8646080760095012</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8673139158576052</v>
+        <v>0.8483009708737864</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.8492935635792779</v>
+        <v>0.7969924812030076</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7912772585669782</v>
+        <v>0.8159806295399515</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7992895204262878</v>
+        <v>0.7979166666666666</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7819225251076041</v>
+        <v>0.8131539611360239</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7903726708074534</v>
+        <v>0.8106904231625836</v>
       </c>
       <c r="V9" t="n">
-        <v>0.712241653418124</v>
+        <v>0.7659574468085106</v>
       </c>
       <c r="W9" t="n">
-        <v>0.7120980091883614</v>
+        <v>0.7117437722419928</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7114427860696517</v>
+        <v>0.7069597069597069</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.6609071274298056</v>
+        <v>0.6948297604035309</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.7034700315457414</v>
+        <v>0.6744868035190617</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.7072727272727273</v>
+        <v>0.6314655172413793</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.3267045454545454</v>
+        <v>0.6907477820025348</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.7789473684210526</v>
+        <v>0.297566371681416</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.8631578947368421</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Gord Perks</t>
+          <t>Shelley Carroll</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9181585677749361</v>
+        <v>0.9184466019417475</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5982142857142857</v>
+        <v>0.7678571428571428</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8768328445747801</v>
+        <v>0.9</v>
       </c>
       <c r="E10" t="n">
-        <v>0.927038626609442</v>
+        <v>0.8508217446270544</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9284692417739628</v>
+        <v>0.8576598311218335</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8788774002954209</v>
+        <v>0.8536285362853628</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7981790591805766</v>
+        <v>0.8393285371702638</v>
       </c>
       <c r="I10" t="n">
-        <v>0.858974358974359</v>
+        <v>0.8929889298892989</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8481203007518797</v>
+        <v>0.8586698337292161</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8558823529411765</v>
+        <v>0.7923832923832924</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8723404255319149</v>
+        <v>0.8656716417910448</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8258164852255054</v>
+        <v>0.8425925925925926</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8357988165680473</v>
+        <v>0.826362484157161</v>
       </c>
       <c r="P10" t="n">
-        <v>0.8237179487179487</v>
+        <v>0.8571428571428572</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.8003120124804992</v>
+        <v>0.7925033467202142</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7722308892355694</v>
+        <v>0.8054830287206266</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7319223985890653</v>
+        <v>0.8094170403587444</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7193732193732194</v>
+        <v>0.8302469135802469</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7021604938271605</v>
+        <v>0.8035928143712575</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6782334384858044</v>
+        <v>0.7539267015706806</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6595744680851063</v>
+        <v>0.6950444726810674</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6138613861386139</v>
+        <v>0.7140974967061924</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.6365591397849462</v>
+        <v>0.6776859504132231</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.6447574334898278</v>
+        <v>0.6808176100628931</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.6086956521739131</v>
+        <v>0.673202614379085</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.2820874471086037</v>
+        <v>0.6870748299319728</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.6631578947368422</v>
+        <v>0.3270142180094787</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.8631578947368421</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Shelley Carroll</t>
+          <t>Gord Perks</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9178082191780822</v>
+        <v>0.9165247018739353</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7678571428571428</v>
+        <v>0.5982142857142857</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8395638629283489</v>
+        <v>0.8743169398907104</v>
       </c>
       <c r="E11" t="n">
-        <v>0.842185128983308</v>
+        <v>0.8786848072562359</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8389057750759878</v>
+        <v>0.9249183895538629</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8869701726844584</v>
+        <v>0.9319955406911928</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8656</v>
+        <v>0.8593073593073592</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8242424242424242</v>
+        <v>0.8802660753880266</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8481203007518797</v>
+        <v>0.8586698337292161</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7746478873239436</v>
+        <v>0.8539823008849557</v>
       </c>
       <c r="M11" t="n">
-        <v>0.8080645161290323</v>
+        <v>0.802937576499388</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8360927152317881</v>
+        <v>0.8290094339622641</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8580441640378549</v>
+        <v>0.8708189158016147</v>
       </c>
       <c r="P11" t="n">
-        <v>0.8357664233576643</v>
+        <v>0.8343057176196033</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.8083333333333333</v>
+        <v>0.7824519230769231</v>
       </c>
       <c r="R11" t="n">
-        <v>0.778702163061564</v>
+        <v>0.7965116279069767</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8268876611418048</v>
+        <v>0.8070175438596492</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7893939393939394</v>
+        <v>0.7492836676217765</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7594108019639935</v>
+        <v>0.743010752688172</v>
       </c>
       <c r="V11" t="n">
-        <v>0.7280405405405406</v>
+        <v>0.7038369304556356</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6720516962843295</v>
+        <v>0.6818700114025085</v>
       </c>
       <c r="X11" t="n">
-        <v>0.6649029982363316</v>
+        <v>0.6682297772567409</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.673202614379085</v>
+        <v>0.6322263222632226</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.7059800664451827</v>
+        <v>0.6162464985994398</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.6821705426356589</v>
+        <v>0.6365591397849462</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.3553223388305847</v>
+        <v>0.6248462484624846</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.8631578947368421</v>
+        <v>0.2726304579339723</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.6631578947368422</v>
       </c>
     </row>
     <row r="12">
@@ -20321,179 +20348,185 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9135135135135135</v>
+        <v>0.9142857142857143</v>
       </c>
       <c r="C12" t="n">
         <v>0.5669642857142857</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8432267884322679</v>
+        <v>0.8932584269662921</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8722139673105498</v>
+        <v>0.8569753810082064</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8531157270029673</v>
+        <v>0.8816234498308906</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8064516129032258</v>
+        <v>0.8604382929642445</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7870662460567823</v>
+        <v>0.8552188552188552</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8444444444444444</v>
+        <v>0.8206896551724138</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8558823529411765</v>
+        <v>0.7923832923832924</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7746478873239436</v>
+        <v>0.8539823008849557</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8278041074249605</v>
+        <v>0.7924050632911392</v>
       </c>
       <c r="N12" t="n">
-        <v>0.807131280388979</v>
+        <v>0.8247549019607843</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7910906298003072</v>
+        <v>0.8414779499404053</v>
       </c>
       <c r="P12" t="n">
-        <v>0.8552188552188552</v>
+        <v>0.8002421307506054</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.8035426731078905</v>
+        <v>0.7887500000000001</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7654723127035831</v>
+        <v>0.8143712574850299</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7067395264116576</v>
+        <v>0.8536585365853658</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7233727810650887</v>
+        <v>0.7304860088365244</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7343999999999999</v>
+        <v>0.7516703786191536</v>
       </c>
       <c r="V12" t="n">
-        <v>0.674342105263158</v>
+        <v>0.7354037267080745</v>
       </c>
       <c r="W12" t="n">
-        <v>0.7109004739336493</v>
+        <v>0.7352245862884161</v>
       </c>
       <c r="X12" t="n">
-        <v>0.6512027491408935</v>
+        <v>0.6723507917174179</v>
       </c>
       <c r="Y12" t="n">
+        <v>0.6730523627075351</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.6589259796806967</v>
+      </c>
+      <c r="AA12" t="n">
         <v>0.6283185840707964</v>
       </c>
-      <c r="Z12" t="n">
-        <v>0.6709677419354838</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0.6378986866791745</v>
-      </c>
       <c r="AB12" t="n">
-        <v>0.2991202346041055</v>
+        <v>0.6590909090909092</v>
       </c>
       <c r="AC12" t="n">
+        <v>0.2969094922737306</v>
+      </c>
+      <c r="AD12" t="n">
         <v>0.6105263157894737</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Paula Fletcher</t>
+          <t>Jennifer McKelvie</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.898876404494382</v>
+        <v>0.9122448979591837</v>
       </c>
       <c r="C13" t="n">
-        <v>0.663677130044843</v>
+        <v>0.8533333333333333</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8840125391849529</v>
+        <v>0.8738738738738738</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9125766871165644</v>
+        <v>0.8753213367609255</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8953846153846154</v>
+        <v>0.8308457711442786</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8542319749216301</v>
+        <v>0.8209331651954603</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8061889250814332</v>
+        <v>0.8546583850931677</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8704268292682926</v>
+        <v>0.861323155216285</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8723404255319149</v>
+        <v>0.8656716417910448</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8080645161290323</v>
+        <v>0.802937576499388</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8278041074249605</v>
+        <v>0.7924050632911392</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>0.8305369127516778</v>
+        <v>0.8634538152610441</v>
       </c>
       <c r="O13" t="n">
-        <v>0.8422712933753943</v>
+        <v>0.8126649076517151</v>
       </c>
       <c r="P13" t="n">
-        <v>0.8268551236749117</v>
+        <v>0.8342175066312998</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.8201680672268907</v>
+        <v>0.7980900409276944</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7636363636363637</v>
+        <v>0.8413978494623656</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7310606060606061</v>
+        <v>0.8614609571788413</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7320061255742726</v>
+        <v>0.839607201309329</v>
       </c>
       <c r="U13" t="n">
-        <v>0.725</v>
+        <v>0.8583743842364532</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6790540540540541</v>
+        <v>0.8276333789329685</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6934426229508197</v>
+        <v>0.7278645833333333</v>
       </c>
       <c r="X13" t="n">
-        <v>0.6550522648083623</v>
+        <v>0.7670682730923695</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.6188340807174888</v>
+        <v>0.7588652482269503</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.6743801652892563</v>
+        <v>0.789983844911147</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.7145969498910676</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.303030303030303</v>
+        <v>0.7655172413793103</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.7096774193548387</v>
+        <v>0.3833943833943834</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.9789473684210527</v>
       </c>
     </row>
     <row r="14">
@@ -20503,812 +20536,839 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8976608187134503</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="C14" t="n">
         <v>0.8310502283105023</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8596774193548387</v>
+        <v>0.8930817610062893</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8526645768025078</v>
+        <v>0.8716981132075472</v>
       </c>
       <c r="F14" t="n">
-        <v>0.839622641509434</v>
+        <v>0.8658682634730539</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8444084278768234</v>
+        <v>0.8448484848484848</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8592964824120604</v>
+        <v>0.8552631578947368</v>
       </c>
       <c r="I14" t="n">
-        <v>0.841692789968652</v>
+        <v>0.8580171358629131</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8258164852255054</v>
+        <v>0.8425925925925926</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8360927152317881</v>
+        <v>0.8290094339622641</v>
       </c>
       <c r="L14" t="n">
-        <v>0.807131280388979</v>
+        <v>0.8247549019607843</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8305369127516778</v>
+        <v>0.8634538152610441</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.826797385620915</v>
+        <v>0.8496815286624204</v>
       </c>
       <c r="P14" t="n">
-        <v>0.864963503649635</v>
+        <v>0.8329048843187661</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.8183391003460208</v>
+        <v>0.8078947368421052</v>
       </c>
       <c r="R14" t="n">
-        <v>0.7938144329896908</v>
+        <v>0.8290155440414508</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7936802973977695</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7821316614420063</v>
+        <v>0.8069381598793364</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7864406779661017</v>
+        <v>0.8133174791914388</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7355516637478108</v>
+        <v>0.7875166002656042</v>
       </c>
       <c r="W14" t="n">
-        <v>0.7008130081300813</v>
+        <v>0.7302955665024631</v>
       </c>
       <c r="X14" t="n">
-        <v>0.6816546762589928</v>
+        <v>0.7281045751633988</v>
       </c>
       <c r="Y14" t="n">
+        <v>0.6925133689839572</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.7362804878048781</v>
+      </c>
+      <c r="AA14" t="n">
         <v>0.6771300448430493</v>
       </c>
-      <c r="Z14" t="n">
-        <v>0.7204116638078902</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0.733201581027668</v>
-      </c>
       <c r="AB14" t="n">
-        <v>0.351937984496124</v>
+        <v>0.6966442953020134</v>
       </c>
       <c r="AC14" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AD14" t="n">
         <v>0.8817204301075269</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Dianne Saxe</t>
+          <t>Paula Fletcher</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8864864864864865</v>
+        <v>0.908411214953271</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7136363636363636</v>
+        <v>0.663677130044843</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8759571209800919</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8488023952095809</v>
+        <v>0.8910648714810282</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8473053892215568</v>
+        <v>0.9178403755868545</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8472222222222222</v>
+        <v>0.895808383233533</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8325434439178515</v>
+        <v>0.8755813953488372</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8330849478390462</v>
+        <v>0.8646080760095012</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8357988165680473</v>
+        <v>0.826362484157161</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8580441640378549</v>
+        <v>0.8708189158016147</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7910906298003072</v>
+        <v>0.8414779499404053</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8422712933753943</v>
+        <v>0.8126649076517151</v>
       </c>
       <c r="N15" t="n">
-        <v>0.826797385620915</v>
+        <v>0.8496815286624204</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7808219178082192</v>
+        <v>0.8439450686641699</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.8248772504091653</v>
+        <v>0.7882653061224489</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7656500802568218</v>
+        <v>0.8234552332912989</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7592592592592593</v>
+        <v>0.8197424892703863</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7533432392273403</v>
+        <v>0.7538699690402477</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7145161290322581</v>
+        <v>0.7686046511627906</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6962233169129721</v>
+        <v>0.727509778357236</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6740858505564388</v>
+        <v>0.7255871446229913</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6454388984509467</v>
+        <v>0.6776232616940582</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.6600441501103753</v>
+        <v>0.6675392670157068</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.6933115823817292</v>
+        <v>0.6521084337349398</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.6461824953445066</v>
+        <v>0.6188340807174888</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.331858407079646</v>
+        <v>0.6540469973890339</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.7526881720430108</v>
+        <v>0.2945914844649021</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.7096774193548387</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Parthi Kandavel</t>
+          <t>Dianne Saxe</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8830188679245283</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
+        <v>0.8851224105461394</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7136363636363636</v>
+      </c>
       <c r="D16" t="n">
-        <v>0.8813559322033898</v>
+        <v>0.8493150684931507</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8446601941747574</v>
+        <v>0.8723926380368098</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8300653594771241</v>
+        <v>0.8525564803804995</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8091872791519434</v>
+        <v>0.8491484184914841</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8641509433962264</v>
+        <v>0.8403755868544601</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8673139158576052</v>
+        <v>0.8483009708737864</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8237179487179487</v>
+        <v>0.8571428571428572</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8357664233576643</v>
+        <v>0.8343057176196033</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8552188552188552</v>
+        <v>0.8002421307506054</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8268551236749117</v>
+        <v>0.8342175066312998</v>
       </c>
       <c r="N16" t="n">
-        <v>0.864963503649635</v>
+        <v>0.8329048843187661</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7808219178082192</v>
+        <v>0.8439450686641699</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.8793103448275862</v>
+        <v>0.7733674775928296</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8063380281690141</v>
+        <v>0.8160919540229885</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8436213991769548</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8376623376623377</v>
+        <v>0.7662538699690402</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8181818181818181</v>
+        <v>0.7622950819672132</v>
       </c>
       <c r="V16" t="n">
-        <v>0.7401315789473684</v>
+        <v>0.71484375</v>
       </c>
       <c r="W16" t="n">
-        <v>0.7491039426523298</v>
+        <v>0.6920199501246882</v>
       </c>
       <c r="X16" t="n">
-        <v>0.7633587786259541</v>
+        <v>0.6879795396419437</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.6721311475409837</v>
+        <v>0.6515957446808511</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.6992481203007519</v>
+        <v>0.6524300441826215</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.775</v>
+        <v>0.6600441501103753</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.342948717948718</v>
-      </c>
-      <c r="AC16" t="inlineStr"/>
+        <v>0.6714471968709257</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.3143189755529686</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.7526881720430108</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Lily Cheng</t>
+          <t>Mike Colle</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8643617021276596</v>
+        <v>0.8667953667953667</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7195767195767195</v>
+        <v>0.7014218009478673</v>
       </c>
       <c r="D17" t="n">
-        <v>0.864951768488746</v>
+        <v>0.9172413793103449</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8367346938775511</v>
+        <v>0.8066581306017926</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8249211356466877</v>
+        <v>0.7992656058751531</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8150572831423896</v>
+        <v>0.79375</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8375209380234506</v>
+        <v>0.8086642599277978</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8492935635792779</v>
+        <v>0.7969924812030076</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8003120124804992</v>
+        <v>0.7925033467202142</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8083333333333333</v>
+        <v>0.7824519230769231</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8035426731078905</v>
+        <v>0.7887500000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8201680672268907</v>
+        <v>0.7980900409276944</v>
       </c>
       <c r="N17" t="n">
-        <v>0.8183391003460208</v>
+        <v>0.8078947368421052</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8248772504091653</v>
+        <v>0.7882653061224489</v>
       </c>
       <c r="P17" t="n">
-        <v>0.8793103448275862</v>
+        <v>0.7733674775928296</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7413194444444444</v>
+        <v>0.7592592592592593</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7702970297029703</v>
+        <v>0.7831858407079646</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7924528301886793</v>
+        <v>0.7523809523809524</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7871621621621622</v>
+        <v>0.7702539298669892</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7267950963222417</v>
+        <v>0.7160161507402423</v>
       </c>
       <c r="W17" t="n">
-        <v>0.7314189189189189</v>
+        <v>0.6961538461538461</v>
       </c>
       <c r="X17" t="n">
-        <v>0.7102966841186736</v>
+        <v>0.7098445595854923</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.6926829268292682</v>
+        <v>0.6858710562414266</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.7057823129251701</v>
+        <v>0.6722306525037935</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.7120315581854043</v>
+        <v>0.624113475177305</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.3716951788491446</v>
+        <v>0.6512261580381471</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.8478260869565217</v>
+        <v>0.3201438848920863</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.7894736842105263</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Mike Colle</t>
+          <t>Lily Cheng</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8579387186629527</v>
+        <v>0.8665480427046264</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7014218009478673</v>
+        <v>0.7195767195767195</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7880258899676376</v>
+        <v>0.8681318681318682</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7804107424960506</v>
+        <v>0.8681318681318682</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7772511848341233</v>
+        <v>0.8368794326241135</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7823240589198036</v>
+        <v>0.8197320341047503</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7949579831932774</v>
+        <v>0.8502358490566038</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7912772585669782</v>
+        <v>0.8159806295399515</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7722308892355694</v>
+        <v>0.8054830287206266</v>
       </c>
       <c r="K18" t="n">
-        <v>0.778702163061564</v>
+        <v>0.7965116279069767</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7654723127035831</v>
+        <v>0.8143712574850299</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7636363636363637</v>
+        <v>0.8413978494623656</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7938144329896908</v>
+        <v>0.8290155440414508</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7656500802568218</v>
+        <v>0.8234552332912989</v>
       </c>
       <c r="P18" t="n">
-        <v>0.8063380281690141</v>
+        <v>0.8160919540229885</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.7413194444444444</v>
+        <v>0.7592592592592593</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7471042471042471</v>
+        <v>0.8669438669438669</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7531446540880503</v>
+        <v>0.7732283464566929</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7193877551020409</v>
+        <v>0.8053927315357562</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7140439932318106</v>
+        <v>0.7822685788787483</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.7652933832709113</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6744604316546763</v>
+        <v>0.7230769230769231</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.624113475177305</v>
+        <v>0.7204161248374512</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.6826758147512865</v>
+        <v>0.7257575757575758</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.678916827852998</v>
+        <v>0.6926829268292682</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.3312597200622084</v>
+        <v>0.6917989417989419</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.3689095127610209</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8478260869565217</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Michael Thompson</t>
+          <t>Parthi Kandavel</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8453237410071942</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.817351598173516</v>
-      </c>
+        <v>0.8646788990825688</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.7710622710622711</v>
+        <v>0.8311688311688312</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7375886524822695</v>
+        <v>0.8565310492505354</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7361853832442068</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7948243992606285</v>
+        <v>0.8256302521008403</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8546845124282982</v>
+        <v>0.8560157790927021</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7992895204262878</v>
+        <v>0.7979166666666666</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7319223985890653</v>
+        <v>0.8094170403587444</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8268876611418048</v>
+        <v>0.8070175438596492</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7067395264116576</v>
+        <v>0.8536585365853658</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7310606060606061</v>
+        <v>0.8614609571788413</v>
       </c>
       <c r="N19" t="n">
-        <v>0.7936802973977695</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7592592592592593</v>
+        <v>0.8197424892703863</v>
       </c>
       <c r="P19" t="n">
-        <v>0.8436213991769548</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.7702970297029703</v>
+        <v>0.7831858407079646</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7471042471042471</v>
+        <v>0.8669438669438669</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8351063829787234</v>
+        <v>0.7988980716253443</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8202676864244742</v>
+        <v>0.8205128205128205</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7250996015936255</v>
+        <v>0.7935483870967742</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6977611940298507</v>
+        <v>0.7638297872340425</v>
       </c>
       <c r="X19" t="n">
-        <v>0.7520325203252033</v>
+        <v>0.7151515151515151</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.7121951219512195</v>
+        <v>0.752808988764045</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.7742782152230971</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.7716186252771619</v>
+        <v>0.6721311475409837</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.4393673110720563</v>
+        <v>0.6801909307875895</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.8404255319148937</v>
-      </c>
+        <v>0.3294346978557505</v>
+      </c>
+      <c r="AD19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Frances Nunziata</t>
+          <t>Michael Thompson</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8149100257069408</v>
+        <v>0.8538461538461538</v>
       </c>
       <c r="C20" t="n">
-        <v>0.875</v>
+        <v>0.817351598173516</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7843426883308715</v>
+        <v>0.8211382113821138</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7363112391930835</v>
+        <v>0.7841079460269865</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7374461979913917</v>
+        <v>0.7612156295224313</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7881481481481482</v>
+        <v>0.7540983606557377</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8669724770642202</v>
+        <v>0.8170028818443804</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7819225251076041</v>
+        <v>0.8131539611360239</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7193732193732194</v>
+        <v>0.8302469135802469</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7893939393939394</v>
+        <v>0.7492836676217765</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7233727810650887</v>
+        <v>0.7304860088365244</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7320061255742726</v>
+        <v>0.839607201309329</v>
       </c>
       <c r="N20" t="n">
-        <v>0.7821316614420063</v>
+        <v>0.8069381598793364</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7533432392273403</v>
+        <v>0.7538699690402477</v>
       </c>
       <c r="P20" t="n">
-        <v>0.8376623376623377</v>
+        <v>0.7662538699690402</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.7924528301886793</v>
+        <v>0.7523809523809524</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7531446540880503</v>
+        <v>0.7732283464566929</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8351063829787234</v>
+        <v>0.7988980716253443</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0.833592534992224</v>
+        <v>0.8369408369408369</v>
       </c>
       <c r="V20" t="n">
-        <v>0.7678855325914149</v>
+        <v>0.8193343898573693</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7140672782874617</v>
+        <v>0.7134238310708899</v>
       </c>
       <c r="X20" t="n">
-        <v>0.7864238410596026</v>
+        <v>0.712</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.7225806451612904</v>
+        <v>0.7377049180327868</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.8147566718995291</v>
+        <v>0.7605893186003683</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.8105646630236794</v>
+        <v>0.7121951219512195</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.4318181818181818</v>
+        <v>0.7331240188383046</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.9473684210526316</v>
+        <v>0.4028571428571428</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8404255319148937</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Nick Mantas</t>
+          <t>Frances Nunziata</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8068181818181819</v>
+        <v>0.8490566037735849</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8403755868544601</v>
+        <v>0.875</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7814992025518341</v>
+        <v>0.8784530386740331</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7180685358255452</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7165109034267914</v>
+        <v>0.7677984665936473</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7588996763754046</v>
+        <v>0.7625979843225084</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8413223140495868</v>
+        <v>0.8015267175572519</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7903726708074534</v>
+        <v>0.8106904231625836</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7021604938271605</v>
+        <v>0.8035928143712575</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7594108019639935</v>
+        <v>0.743010752688172</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7343999999999999</v>
+        <v>0.7516703786191536</v>
       </c>
       <c r="M21" t="n">
-        <v>0.725</v>
+        <v>0.8583743842364532</v>
       </c>
       <c r="N21" t="n">
-        <v>0.7864406779661017</v>
+        <v>0.8133174791914388</v>
       </c>
       <c r="O21" t="n">
-        <v>0.7145161290322581</v>
+        <v>0.7686046511627906</v>
       </c>
       <c r="P21" t="n">
-        <v>0.8181818181818181</v>
+        <v>0.7622950819672132</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.7871621621621622</v>
+        <v>0.7702539298669892</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7193877551020409</v>
+        <v>0.8053927315357562</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8202676864244742</v>
+        <v>0.8205128205128205</v>
       </c>
       <c r="T21" t="n">
-        <v>0.833592534992224</v>
+        <v>0.8369408369408369</v>
       </c>
       <c r="U21" t="n">
         <v>1</v>
       </c>
       <c r="V21" t="n">
-        <v>0.7374784110535406</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7350993377483444</v>
+        <v>0.7416762342135477</v>
       </c>
       <c r="X21" t="n">
-        <v>0.7621621621621621</v>
+        <v>0.7520661157024793</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.7009345794392523</v>
+        <v>0.7762669962917181</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.7834179357021996</v>
+        <v>0.7997179125528914</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.8058252427184466</v>
+        <v>0.7225806451612904</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.443076923076923</v>
+        <v>0.7854500616522812</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.9361702127659575</v>
+        <v>0.4023605150214592</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.9473684210526316</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Jon Burnside</t>
+          <t>Nick Mantas</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7594202898550725</v>
+        <v>0.7893700787401575</v>
       </c>
       <c r="C22" t="n">
-        <v>0.755868544600939</v>
+        <v>0.8403755868544601</v>
       </c>
       <c r="D22" t="n">
-        <v>0.7263843648208469</v>
+        <v>0.7730496453900709</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6869009584664536</v>
+        <v>0.7735368956743003</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6773162939297125</v>
+        <v>0.7200488997555012</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7168874172185431</v>
+        <v>0.71875</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7804054054054054</v>
+        <v>0.7859733978234583</v>
       </c>
       <c r="I22" t="n">
-        <v>0.712241653418124</v>
+        <v>0.7659574468085106</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6782334384858044</v>
+        <v>0.7539267015706806</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7280405405405406</v>
+        <v>0.7038369304556356</v>
       </c>
       <c r="L22" t="n">
-        <v>0.674342105263158</v>
+        <v>0.7354037267080745</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6790540540540541</v>
+        <v>0.8276333789329685</v>
       </c>
       <c r="N22" t="n">
-        <v>0.7355516637478108</v>
+        <v>0.7875166002656042</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6962233169129721</v>
+        <v>0.727509778357236</v>
       </c>
       <c r="P22" t="n">
-        <v>0.7401315789473684</v>
+        <v>0.71484375</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.7267950963222417</v>
+        <v>0.7160161507402423</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7140439932318106</v>
+        <v>0.7822685788787483</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7250996015936255</v>
+        <v>0.7935483870967742</v>
       </c>
       <c r="T22" t="n">
-        <v>0.7678855325914149</v>
+        <v>0.8193343898573693</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7374784110535406</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="V22" t="n">
         <v>1</v>
       </c>
       <c r="W22" t="n">
-        <v>0.6626916524701874</v>
+        <v>0.7285531370038412</v>
       </c>
       <c r="X22" t="n">
-        <v>0.7330895795246801</v>
+        <v>0.7307692307692308</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.6823821339950372</v>
+        <v>0.7590027700831025</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.7460595446584939</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.7421150278293136</v>
+        <v>0.7009345794392523</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.4386792452830188</v>
+        <v>0.7745901639344263</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.8202247191011236</v>
+        <v>0.4258373205741627</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.9361702127659575</v>
       </c>
     </row>
     <row r="23">
@@ -21318,629 +21378,740 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7409470752089137</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="C23" t="n">
         <v>0.7014218009478673</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6942277691107644</v>
+        <v>0.7988505747126436</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6804915514592934</v>
+        <v>0.7232250300842359</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6625766871165644</v>
+        <v>0.7127906976744186</v>
       </c>
       <c r="G23" t="n">
-        <v>0.6820349761526232</v>
+        <v>0.6868327402135231</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7079934747145187</v>
+        <v>0.7349537037037037</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7120980091883614</v>
+        <v>0.7117437722419928</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6595744680851063</v>
+        <v>0.6950444726810674</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6720516962843295</v>
+        <v>0.6818700114025085</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7109004739336493</v>
+        <v>0.7352245862884161</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6934426229508197</v>
+        <v>0.7278645833333333</v>
       </c>
       <c r="N23" t="n">
-        <v>0.7008130081300813</v>
+        <v>0.7302955665024631</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6740858505564388</v>
+        <v>0.7255871446229913</v>
       </c>
       <c r="P23" t="n">
-        <v>0.7491039426523298</v>
+        <v>0.6920199501246882</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.7314189189189189</v>
+        <v>0.6961538461538461</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.7652933832709113</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6977611940298507</v>
+        <v>0.7638297872340425</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7140672782874617</v>
+        <v>0.7134238310708899</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7350993377483444</v>
+        <v>0.7416762342135477</v>
       </c>
       <c r="V23" t="n">
-        <v>0.6626916524701874</v>
+        <v>0.7285531370038412</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>0.721830985915493</v>
+        <v>0.6578947368421053</v>
       </c>
       <c r="Y23" t="n">
+        <v>0.722875816993464</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0.724188790560472</v>
+      </c>
+      <c r="AA23" t="n">
         <v>0.6433408577878104</v>
       </c>
-      <c r="Z23" t="n">
-        <v>0.6941176470588235</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0.7088122605363985</v>
-      </c>
       <c r="AB23" t="n">
-        <v>0.406060606060606</v>
+        <v>0.6828309305373526</v>
       </c>
       <c r="AC23" t="n">
+        <v>0.3902161547212741</v>
+      </c>
+      <c r="AD23" t="n">
         <v>0.6914893617021276</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>James Pasternak</t>
+          <t>Jon Burnside</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7048710601719197</v>
+        <v>0.724907063197026</v>
       </c>
       <c r="C24" t="n">
-        <v>0.778894472361809</v>
+        <v>0.755868544600939</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6832191780821918</v>
+        <v>0.7183908045977012</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6456953642384107</v>
+        <v>0.7151741293532339</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6378737541528239</v>
+        <v>0.6830143540669856</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6734348561759729</v>
+        <v>0.6654366543665436</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7548500881834215</v>
+        <v>0.7035714285714285</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7114427860696517</v>
+        <v>0.7069597069597069</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6138613861386139</v>
+        <v>0.7140974967061924</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6649029982363316</v>
+        <v>0.6682297772567409</v>
       </c>
       <c r="L24" t="n">
-        <v>0.6512027491408935</v>
+        <v>0.6723507917174179</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6550522648083623</v>
+        <v>0.7670682730923695</v>
       </c>
       <c r="N24" t="n">
-        <v>0.6816546762589928</v>
+        <v>0.7281045751633988</v>
       </c>
       <c r="O24" t="n">
-        <v>0.6454388984509467</v>
+        <v>0.6776232616940582</v>
       </c>
       <c r="P24" t="n">
-        <v>0.7633587786259541</v>
+        <v>0.6879795396419437</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.7102966841186736</v>
+        <v>0.7098445595854923</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6744604316546763</v>
+        <v>0.7230769230769231</v>
       </c>
       <c r="S24" t="n">
-        <v>0.7520325203252033</v>
+        <v>0.7151515151515151</v>
       </c>
       <c r="T24" t="n">
-        <v>0.7864238410596026</v>
+        <v>0.712</v>
       </c>
       <c r="U24" t="n">
-        <v>0.7621621621621621</v>
+        <v>0.7520661157024793</v>
       </c>
       <c r="V24" t="n">
-        <v>0.7330895795246801</v>
+        <v>0.7307692307692308</v>
       </c>
       <c r="W24" t="n">
-        <v>0.721830985915493</v>
+        <v>0.6578947368421053</v>
       </c>
       <c r="X24" t="n">
         <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.7139303482587065</v>
+        <v>0.739247311827957</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.7419354838709677</v>
+        <v>0.7210982658959537</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.7930327868852459</v>
+        <v>0.6823821339950372</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.4588815789473685</v>
+        <v>0.7394843962008142</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.7934782608695652</v>
+        <v>0.4409356725146198</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8202247191011236</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Jaye Robinson</t>
+          <t>James Pasternak</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6787564766839378</v>
+        <v>0.7151051625239006</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7136363636363636</v>
+        <v>0.778894472361809</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6490066225165563</v>
+        <v>0.7469135802469136</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6379310344827587</v>
+        <v>0.6981627296587927</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6314655172413793</v>
+        <v>0.6662515566625156</v>
       </c>
       <c r="G25" t="n">
-        <v>0.6314655172413793</v>
+        <v>0.6470588235294117</v>
       </c>
       <c r="H25" t="n">
-        <v>0.7145969498910676</v>
+        <v>0.7235367372353674</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6609071274298056</v>
+        <v>0.6948297604035309</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6365591397849462</v>
+        <v>0.6776859504132231</v>
       </c>
       <c r="K25" t="n">
-        <v>0.673202614379085</v>
+        <v>0.6322263222632226</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6283185840707964</v>
+        <v>0.6730523627075351</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6188340807174888</v>
+        <v>0.7588652482269503</v>
       </c>
       <c r="N25" t="n">
-        <v>0.6771300448430493</v>
+        <v>0.6925133689839572</v>
       </c>
       <c r="O25" t="n">
-        <v>0.6600441501103753</v>
+        <v>0.6675392670157068</v>
       </c>
       <c r="P25" t="n">
-        <v>0.6721311475409837</v>
+        <v>0.6515957446808511</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.6926829268292682</v>
+        <v>0.6858710562414266</v>
       </c>
       <c r="R25" t="n">
-        <v>0.624113475177305</v>
+        <v>0.7204161248374512</v>
       </c>
       <c r="S25" t="n">
-        <v>0.7121951219512195</v>
+        <v>0.752808988764045</v>
       </c>
       <c r="T25" t="n">
-        <v>0.7225806451612904</v>
+        <v>0.7377049180327868</v>
       </c>
       <c r="U25" t="n">
-        <v>0.7009345794392523</v>
+        <v>0.7762669962917181</v>
       </c>
       <c r="V25" t="n">
-        <v>0.6823821339950372</v>
+        <v>0.7590027700831025</v>
       </c>
       <c r="W25" t="n">
-        <v>0.6433408577878104</v>
+        <v>0.722875816993464</v>
       </c>
       <c r="X25" t="n">
-        <v>0.7139303482587065</v>
+        <v>0.739247311827957</v>
       </c>
       <c r="Y25" t="n">
         <v>1</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.7113163972286374</v>
+        <v>0.7852664576802508</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.7306666666666667</v>
+        <v>0.7139303482587065</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.5331905781584583</v>
+        <v>0.7469050894085282</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.7096774193548387</v>
+        <v>0.4527607361963191</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.7934782608695652</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Brad Bradford</t>
+          <t>Vincent Crisanti</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6780626780626781</v>
+        <v>0.6943127962085308</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8486238532110092</v>
+        <v>0.8634146341463415</v>
       </c>
       <c r="D26" t="n">
-        <v>0.7163695299837926</v>
+        <v>0.7258064516129032</v>
       </c>
       <c r="E26" t="n">
-        <v>0.665086887835703</v>
+        <v>0.7004405286343612</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6582677165354331</v>
+        <v>0.6481481481481481</v>
       </c>
       <c r="G26" t="n">
-        <v>0.7071197411003236</v>
+        <v>0.629737609329446</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7953410981697171</v>
+        <v>0.7102672292545711</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7034700315457414</v>
+        <v>0.6744868035190617</v>
       </c>
       <c r="J26" t="n">
-        <v>0.6447574334898278</v>
+        <v>0.6808176100628931</v>
       </c>
       <c r="K26" t="n">
-        <v>0.7059800664451827</v>
+        <v>0.6162464985994398</v>
       </c>
       <c r="L26" t="n">
-        <v>0.6709677419354838</v>
+        <v>0.6589259796806967</v>
       </c>
       <c r="M26" t="n">
-        <v>0.6743801652892563</v>
+        <v>0.789983844911147</v>
       </c>
       <c r="N26" t="n">
-        <v>0.7204116638078902</v>
+        <v>0.7362804878048781</v>
       </c>
       <c r="O26" t="n">
-        <v>0.6933115823817292</v>
+        <v>0.6521084337349398</v>
       </c>
       <c r="P26" t="n">
-        <v>0.6992481203007519</v>
+        <v>0.6524300441826215</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.7057823129251701</v>
+        <v>0.6722306525037935</v>
       </c>
       <c r="R26" t="n">
-        <v>0.6826758147512865</v>
+        <v>0.7257575757575758</v>
       </c>
       <c r="S26" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.7742782152230971</v>
       </c>
       <c r="T26" t="n">
-        <v>0.8147566718995291</v>
+        <v>0.7605893186003683</v>
       </c>
       <c r="U26" t="n">
-        <v>0.7834179357021996</v>
+        <v>0.7997179125528914</v>
       </c>
       <c r="V26" t="n">
-        <v>0.7460595446584939</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="W26" t="n">
-        <v>0.6941176470588235</v>
+        <v>0.724188790560472</v>
       </c>
       <c r="X26" t="n">
-        <v>0.7419354838709677</v>
+        <v>0.7210982658959537</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.7113163972286374</v>
+        <v>0.7852664576802508</v>
       </c>
       <c r="Z26" t="n">
         <v>1</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.77734375</v>
+        <v>0.7306666666666667</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.500780031201248</v>
+        <v>0.778816199376947</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.9368421052631579</v>
+        <v>0.4748603351955307</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.9111111111111111</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Vincent Crisanti</t>
+          <t>Jaye Robinson</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.667844522968198</v>
+        <v>0.6787564766839378</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8634146341463415</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.6962962962962963</v>
-      </c>
+        <v>0.7136363636363636</v>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
-        <v>0.6290909090909091</v>
+        <v>0.6490066225165563</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6160877513711152</v>
+        <v>0.6379310344827587</v>
       </c>
       <c r="G27" t="n">
-        <v>0.666030534351145</v>
+        <v>0.6314655172413793</v>
       </c>
       <c r="H27" t="n">
-        <v>0.7934362934362934</v>
+        <v>0.6609071274298056</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7072727272727273</v>
+        <v>0.6314655172413793</v>
       </c>
       <c r="J27" t="n">
-        <v>0.6086956521739131</v>
+        <v>0.673202614379085</v>
       </c>
       <c r="K27" t="n">
-        <v>0.6821705426356589</v>
+        <v>0.6365591397849462</v>
       </c>
       <c r="L27" t="n">
-        <v>0.6378986866791745</v>
+        <v>0.6283185840707964</v>
       </c>
       <c r="M27" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.7145969498910676</v>
       </c>
       <c r="N27" t="n">
-        <v>0.733201581027668</v>
+        <v>0.6771300448430493</v>
       </c>
       <c r="O27" t="n">
-        <v>0.6461824953445066</v>
+        <v>0.6188340807174888</v>
       </c>
       <c r="P27" t="n">
-        <v>0.775</v>
+        <v>0.6600441501103753</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.7120315581854043</v>
+        <v>0.624113475177305</v>
       </c>
       <c r="R27" t="n">
-        <v>0.678916827852998</v>
+        <v>0.6926829268292682</v>
       </c>
       <c r="S27" t="n">
-        <v>0.7716186252771619</v>
+        <v>0.6721311475409837</v>
       </c>
       <c r="T27" t="n">
-        <v>0.8105646630236794</v>
+        <v>0.7121951219512195</v>
       </c>
       <c r="U27" t="n">
-        <v>0.8058252427184466</v>
+        <v>0.7225806451612904</v>
       </c>
       <c r="V27" t="n">
-        <v>0.7421150278293136</v>
+        <v>0.7009345794392523</v>
       </c>
       <c r="W27" t="n">
-        <v>0.7088122605363985</v>
+        <v>0.6433408577878104</v>
       </c>
       <c r="X27" t="n">
-        <v>0.7930327868852459</v>
+        <v>0.6823821339950372</v>
       </c>
       <c r="Y27" t="n">
+        <v>0.7139303482587065</v>
+      </c>
+      <c r="Z27" t="n">
         <v>0.7306666666666667</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0.77734375</v>
       </c>
       <c r="AA27" t="n">
         <v>1</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.4873646209386282</v>
+        <v>0.7113163972286374</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.9111111111111111</v>
+        <v>0.5331905781584583</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.7096774193548387</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Stephen Holyday</t>
+          <t>Brad Bradford</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.268542199488491</v>
+        <v>0.6600397614314115</v>
       </c>
       <c r="C28" t="n">
-        <v>0.5663716814159292</v>
+        <v>0.8486238532110092</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.6043165467625899</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2767475035663338</v>
+        <v>0.6971649484536082</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2781740370898717</v>
+        <v>0.6458072590738423</v>
       </c>
       <c r="G28" t="n">
-        <v>0.3078055964653903</v>
+        <v>0.6304347826086957</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3903177004538578</v>
+        <v>0.6811414392059554</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3267045454545454</v>
+        <v>0.6907477820025348</v>
       </c>
       <c r="J28" t="n">
-        <v>0.2820874471086037</v>
+        <v>0.6870748299319728</v>
       </c>
       <c r="K28" t="n">
-        <v>0.3553223388305847</v>
+        <v>0.6248462484624846</v>
       </c>
       <c r="L28" t="n">
-        <v>0.2991202346041055</v>
+        <v>0.6590909090909092</v>
       </c>
       <c r="M28" t="n">
-        <v>0.303030303030303</v>
+        <v>0.7655172413793103</v>
       </c>
       <c r="N28" t="n">
-        <v>0.351937984496124</v>
+        <v>0.6966442953020134</v>
       </c>
       <c r="O28" t="n">
-        <v>0.331858407079646</v>
+        <v>0.6540469973890339</v>
       </c>
       <c r="P28" t="n">
-        <v>0.342948717948718</v>
+        <v>0.6714471968709257</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.3716951788491446</v>
+        <v>0.6512261580381471</v>
       </c>
       <c r="R28" t="n">
-        <v>0.3312597200622084</v>
+        <v>0.6917989417989419</v>
       </c>
       <c r="S28" t="n">
-        <v>0.4393673110720563</v>
+        <v>0.6801909307875895</v>
       </c>
       <c r="T28" t="n">
-        <v>0.4318181818181818</v>
+        <v>0.7331240188383046</v>
       </c>
       <c r="U28" t="n">
-        <v>0.443076923076923</v>
+        <v>0.7854500616522812</v>
       </c>
       <c r="V28" t="n">
-        <v>0.4386792452830188</v>
+        <v>0.7745901639344263</v>
       </c>
       <c r="W28" t="n">
-        <v>0.406060606060606</v>
+        <v>0.6828309305373526</v>
       </c>
       <c r="X28" t="n">
-        <v>0.4588815789473685</v>
+        <v>0.7394843962008142</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.5331905781584583</v>
+        <v>0.7469050894085282</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.500780031201248</v>
+        <v>0.778816199376947</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.4873646209386282</v>
+        <v>0.7113163972286374</v>
       </c>
       <c r="AB28" t="n">
         <v>1</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.3789473684210526</v>
+        <v>0.501840490797546</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9368421052631579</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
+          <t>Stephen Holyday</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.2589437819420783</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.5663716814159292</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.2841530054644809</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.3201357466063348</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.2736156351791531</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.2669632925472748</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.306695464362851</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.297566371681416</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.3270142180094787</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.2726304579339723</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.2969094922737306</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.3833943833943834</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.2945914844649021</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.3143189755529686</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.3201438848920863</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.3689095127610209</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.3294346978557505</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.4028571428571428</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.4023605150214592</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.4258373205741627</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.3902161547212741</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0.4409356725146198</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0.4527607361963191</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.4748603351955307</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.5331905781584583</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.501840490797546</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.3789473684210526</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
           <t>John Tory</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="n">
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="n">
         <v>0.9263157894736842</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="n">
         <v>0.8526315789473684</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F30" t="n">
         <v>0.7065217391304348</v>
       </c>
-      <c r="F29" t="n">
+      <c r="G30" t="n">
         <v>0.7157894736842105</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H30" t="n">
+        <v>0.7789473684210526</v>
+      </c>
+      <c r="I30" t="n">
         <v>0.8631578947368421</v>
       </c>
-      <c r="H29" t="n">
+      <c r="J30" t="n">
+        <v>0.8631578947368421</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.6631578947368422</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.6105263157894737</v>
+      </c>
+      <c r="M30" t="n">
         <v>0.9789473684210527</v>
       </c>
-      <c r="I29" t="n">
-        <v>0.7789473684210526</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.6631578947368422</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0.8631578947368421</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0.6105263157894737</v>
-      </c>
-      <c r="M29" t="n">
+      <c r="N30" t="n">
+        <v>0.8817204301075269</v>
+      </c>
+      <c r="O30" t="n">
         <v>0.7096774193548387</v>
       </c>
-      <c r="N29" t="n">
-        <v>0.8817204301075269</v>
-      </c>
-      <c r="O29" t="n">
+      <c r="P30" t="n">
         <v>0.7526881720430108</v>
       </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="n">
+      <c r="Q30" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="R30" t="n">
         <v>0.8478260869565217</v>
       </c>
-      <c r="R29" t="n">
-        <v>0.7894736842105263</v>
-      </c>
-      <c r="S29" t="n">
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="n">
         <v>0.8404255319148937</v>
       </c>
-      <c r="T29" t="n">
+      <c r="U30" t="n">
         <v>0.9473684210526316</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V30" t="n">
         <v>0.9361702127659575</v>
       </c>
-      <c r="V29" t="n">
+      <c r="W30" t="n">
+        <v>0.6914893617021276</v>
+      </c>
+      <c r="X30" t="n">
         <v>0.8202247191011236</v>
       </c>
-      <c r="W29" t="n">
-        <v>0.6914893617021276</v>
-      </c>
-      <c r="X29" t="n">
+      <c r="Y30" t="n">
         <v>0.7934782608695652</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="Z30" t="n">
+        <v>0.9111111111111111</v>
+      </c>
+      <c r="AA30" t="n">
         <v>0.7096774193548387</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AB30" t="n">
         <v>0.9368421052631579</v>
       </c>
-      <c r="AA29" t="n">
-        <v>0.9111111111111111</v>
-      </c>
-      <c r="AB29" t="n">
+      <c r="AC30" t="n">
         <v>0.3789473684210526</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AD30" t="n">
         <v>1</v>
       </c>
     </row>
